--- a/grupos/4ALCM - Estadisticos 20212.xlsx
+++ b/grupos/4ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -197,18 +197,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Santiago Hernández Mariana</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Santiago Hernández Mariana</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -227,6 +227,69 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>LARRINAGA</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>SANTES</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>GONZALO FEDERICO</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>ERIKA</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
+  </si>
+  <si>
     <t>ALVARADO</t>
   </si>
   <si>
@@ -239,9 +302,6 @@
     <t>BERISTAIN</t>
   </si>
   <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
     <t>CASTELLANOS</t>
   </si>
   <si>
@@ -272,21 +332,12 @@
     <t>LASTRE</t>
   </si>
   <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
     <t>LIMA</t>
   </si>
   <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
     <t>MARIANO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MACARIO</t>
   </si>
   <si>
@@ -296,18 +347,12 @@
     <t>OLTEHUA</t>
   </si>
   <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
     <t>ROMAN</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -317,9 +362,6 @@
     <t>VARGAS</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -329,9 +371,6 @@
     <t>APALE</t>
   </si>
   <si>
-    <t>SORIA</t>
-  </si>
-  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
@@ -359,39 +398,24 @@
     <t>ENRIQUEZ</t>
   </si>
   <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
     <t>PACHECO</t>
   </si>
   <si>
-    <t>SANTES</t>
-  </si>
-  <si>
     <t>MARINERO</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -416,9 +440,6 @@
     <t>JOSE ISAIAS</t>
   </si>
   <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
     <t>JENNIFER</t>
   </si>
   <si>
@@ -455,15 +476,9 @@
     <t>ATENEA</t>
   </si>
   <si>
-    <t>GONZALO FEDERICO</t>
-  </si>
-  <si>
     <t>MERARY MADAY</t>
   </si>
   <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
     <t>JAQUELINE</t>
   </si>
   <si>
@@ -473,18 +488,12 @@
     <t>PERLA MARITZA</t>
   </si>
   <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
     <t>ITZEL</t>
   </si>
   <si>
     <t>LISBETH ESMERALDA</t>
   </si>
   <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
     <t>FERNANDO VADHIR</t>
   </si>
   <si>
@@ -494,9 +503,6 @@
     <t>FABIOLA</t>
   </si>
   <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
     <t>ARLET</t>
   </si>
   <si>
@@ -507,12 +513,6 @@
   </si>
   <si>
     <t>SELINA</t>
-  </si>
-  <si>
-    <t>ERIKA</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
   </si>
 </sst>
 </file>
@@ -1017,10 +1017,10 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -1080,10 +1080,10 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -1106,10 +1106,10 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1169,10 +1169,10 @@
         <v>6</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -1195,10 +1195,10 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -1258,10 +1258,10 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z6">
         <v>10</v>
@@ -1284,10 +1284,10 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>7</v>
@@ -1347,10 +1347,10 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>7</v>
@@ -1462,10 +1462,10 @@
         <v>9</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -1525,10 +1525,10 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <v>10</v>
@@ -1551,10 +1551,10 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1614,10 +1614,10 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>9</v>
@@ -1640,10 +1640,10 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -1703,10 +1703,10 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z11">
         <v>8</v>
@@ -1818,10 +1818,10 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -1881,10 +1881,10 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <v>10</v>
@@ -1907,10 +1907,10 @@
         <v>6</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>7</v>
@@ -1970,10 +1970,10 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -1996,10 +1996,10 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -2059,10 +2059,10 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z15">
         <v>10</v>
@@ -2085,10 +2085,10 @@
         <v>5</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>8</v>
@@ -2148,10 +2148,10 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>8</v>
@@ -2174,10 +2174,10 @@
         <v>9</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -2237,10 +2237,10 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z17">
         <v>10</v>
@@ -2263,10 +2263,10 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E18">
         <v>7</v>
@@ -2326,10 +2326,10 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z18">
         <v>7</v>
@@ -2352,10 +2352,10 @@
         <v>10</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -2415,10 +2415,10 @@
         <v>10</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2441,10 +2441,10 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -2504,10 +2504,10 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z20">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>-1</v>
@@ -2593,7 +2593,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -2619,10 +2619,10 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>5</v>
@@ -2682,10 +2682,10 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2708,10 +2708,10 @@
         <v>9</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -2771,10 +2771,10 @@
         <v>9</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z23">
         <v>10</v>
@@ -2797,10 +2797,10 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>8</v>
@@ -2860,10 +2860,10 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>8</v>
@@ -2886,10 +2886,10 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>5</v>
@@ -2949,10 +2949,10 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>5</v>
@@ -2975,10 +2975,10 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E26">
         <v>10</v>
@@ -3038,10 +3038,10 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>10</v>
@@ -3064,7 +3064,7 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D27">
         <v>-1</v>
@@ -3127,7 +3127,7 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>-1</v>
@@ -3153,7 +3153,7 @@
         <v>5</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <v>-1</v>
@@ -3216,7 +3216,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>-1</v>
@@ -3242,10 +3242,10 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>5</v>
@@ -3305,10 +3305,10 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>5</v>
@@ -3331,10 +3331,10 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E30">
         <v>10</v>
@@ -3394,10 +3394,10 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z30">
         <v>10</v>
@@ -3420,7 +3420,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D31">
         <v>-1</v>
@@ -3483,7 +3483,7 @@
         <v>6</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>-1</v>
@@ -3509,10 +3509,10 @@
         <v>9</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E32">
         <v>10</v>
@@ -3572,10 +3572,10 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z32">
         <v>10</v>
@@ -3598,10 +3598,10 @@
         <v>9</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E33">
         <v>9</v>
@@ -3661,10 +3661,10 @@
         <v>9</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z33">
         <v>9</v>
@@ -3687,10 +3687,10 @@
         <v>8</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -3750,10 +3750,10 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>6</v>
@@ -3776,10 +3776,10 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E35">
         <v>7</v>
@@ -3839,10 +3839,10 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z35">
         <v>7</v>
@@ -3865,10 +3865,10 @@
         <v>8</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E36">
         <v>6</v>
@@ -3928,10 +3928,10 @@
         <v>8</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z36">
         <v>6</v>
@@ -3954,10 +3954,10 @@
         <v>10</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E37">
         <v>10</v>
@@ -4017,10 +4017,10 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z37">
         <v>10</v>
@@ -4043,10 +4043,10 @@
         <v>9</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E38">
         <v>10</v>
@@ -4106,10 +4106,10 @@
         <v>9</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z38">
         <v>10</v>
@@ -4135,7 +4135,7 @@
         <v>-1</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E39">
         <v>10</v>
@@ -4198,7 +4198,7 @@
         <v>-1</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z39">
         <v>10</v>
@@ -4355,7 +4355,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
@@ -4364,27 +4364,30 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>81.08</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
+      </c>
       <c r="I2">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -4393,27 +4396,30 @@
         <v>37</v>
       </c>
       <c r="D3">
+        <v>31</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>83.78</v>
+      </c>
+      <c r="G3">
+        <v>16.22</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>37</v>
-      </c>
-      <c r="J3">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -4422,19 +4428,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>83.78</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="G4">
-        <v>16.22</v>
+        <v>13.51</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4445,7 +4451,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -4454,25 +4460,25 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>86.48999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="G5">
-        <v>13.51</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4578,7 +4584,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4607,59 +4613,59 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920187</v>
+        <v>20330051920222</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920187</v>
+        <v>20330051920222</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920220</v>
+        <v>20330051920234</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>59</v>
@@ -4667,39 +4673,39 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920220</v>
+        <v>20330051920236</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920221</v>
+        <v>20330051920240</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>59</v>
@@ -4707,1382 +4713,122 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920221</v>
+        <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920374</v>
+        <v>20330051920251</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920374</v>
+        <v>20330051920251</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920222</v>
+        <v>20330051920258</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920222</v>
+        <v>20330051920259</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920223</v>
+        <v>20330051920259</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920223</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>133</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920224</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920224</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920225</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920225</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920375</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920375</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920226</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920226</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920227</v>
-      </c>
-      <c r="B22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" t="s">
-        <v>138</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920227</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920228</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920228</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920229</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" t="s">
-        <v>140</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920229</v>
-      </c>
-      <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920230</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920230</v>
-      </c>
-      <c r="B29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920231</v>
-      </c>
-      <c r="B30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" t="s">
-        <v>142</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920231</v>
-      </c>
-      <c r="B31" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920232</v>
-      </c>
-      <c r="B32" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" t="s">
-        <v>143</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920232</v>
-      </c>
-      <c r="B33" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920233</v>
-      </c>
-      <c r="B34" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920233</v>
-      </c>
-      <c r="B35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" t="s">
-        <v>144</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920234</v>
-      </c>
-      <c r="B36" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" t="s">
-        <v>115</v>
-      </c>
-      <c r="D36" t="s">
-        <v>145</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920234</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" t="s">
-        <v>145</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920376</v>
-      </c>
-      <c r="B38" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" t="s">
-        <v>146</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920376</v>
-      </c>
-      <c r="B39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" t="s">
-        <v>116</v>
-      </c>
-      <c r="D39" t="s">
-        <v>146</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920236</v>
-      </c>
-      <c r="B40" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D40" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920236</v>
-      </c>
-      <c r="B41" t="s">
-        <v>86</v>
-      </c>
-      <c r="C41" t="s">
-        <v>117</v>
-      </c>
-      <c r="D41" t="s">
-        <v>147</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920237</v>
-      </c>
-      <c r="B42" t="s">
-        <v>87</v>
-      </c>
-      <c r="C42" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" t="s">
-        <v>148</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920237</v>
-      </c>
-      <c r="B43" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" t="s">
-        <v>148</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920238</v>
-      </c>
-      <c r="B44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" t="s">
-        <v>149</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920238</v>
-      </c>
-      <c r="B45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" t="s">
-        <v>119</v>
-      </c>
-      <c r="D45" t="s">
-        <v>149</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920239</v>
-      </c>
-      <c r="B46" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46" t="s">
-        <v>150</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920239</v>
-      </c>
-      <c r="B47" t="s">
-        <v>89</v>
-      </c>
-      <c r="C47" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" t="s">
-        <v>150</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920240</v>
-      </c>
-      <c r="B48" t="s">
-        <v>88</v>
-      </c>
-      <c r="C48" t="s">
-        <v>120</v>
-      </c>
-      <c r="D48" t="s">
-        <v>151</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920240</v>
-      </c>
-      <c r="B49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" t="s">
-        <v>120</v>
-      </c>
-      <c r="D49" t="s">
-        <v>151</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920241</v>
-      </c>
-      <c r="B50" t="s">
-        <v>90</v>
-      </c>
-      <c r="C50" t="s">
-        <v>121</v>
-      </c>
-      <c r="D50" t="s">
-        <v>152</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920241</v>
-      </c>
-      <c r="B51" t="s">
-        <v>90</v>
-      </c>
-      <c r="C51" t="s">
-        <v>121</v>
-      </c>
-      <c r="D51" t="s">
-        <v>152</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920243</v>
-      </c>
-      <c r="B52" t="s">
-        <v>91</v>
-      </c>
-      <c r="C52" t="s">
-        <v>78</v>
-      </c>
-      <c r="D52" t="s">
-        <v>153</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920243</v>
-      </c>
-      <c r="B53" t="s">
-        <v>91</v>
-      </c>
-      <c r="C53" t="s">
-        <v>78</v>
-      </c>
-      <c r="D53" t="s">
-        <v>153</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920244</v>
-      </c>
-      <c r="B54" t="s">
-        <v>92</v>
-      </c>
-      <c r="C54" t="s">
-        <v>113</v>
-      </c>
-      <c r="D54" t="s">
-        <v>154</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920244</v>
-      </c>
-      <c r="B55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" t="s">
-        <v>113</v>
-      </c>
-      <c r="D55" t="s">
-        <v>154</v>
-      </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920248</v>
-      </c>
-      <c r="B56" t="s">
-        <v>93</v>
-      </c>
-      <c r="C56" t="s">
-        <v>81</v>
-      </c>
-      <c r="D56" t="s">
-        <v>155</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920248</v>
-      </c>
-      <c r="B57" t="s">
-        <v>93</v>
-      </c>
-      <c r="C57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D57" t="s">
-        <v>155</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920249</v>
-      </c>
-      <c r="B58" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" t="s">
-        <v>122</v>
-      </c>
-      <c r="D58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920249</v>
-      </c>
-      <c r="B59" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" t="s">
-        <v>122</v>
-      </c>
-      <c r="D59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920250</v>
-      </c>
-      <c r="B60" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" t="s">
-        <v>118</v>
-      </c>
-      <c r="D60" t="s">
-        <v>157</v>
-      </c>
-      <c r="E60" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920250</v>
-      </c>
-      <c r="B61" t="s">
-        <v>94</v>
-      </c>
-      <c r="C61" t="s">
-        <v>118</v>
-      </c>
-      <c r="D61" t="s">
-        <v>157</v>
-      </c>
-      <c r="E61" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920251</v>
-      </c>
-      <c r="B62" t="s">
-        <v>95</v>
-      </c>
-      <c r="C62" t="s">
-        <v>123</v>
-      </c>
-      <c r="D62" t="s">
-        <v>158</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920251</v>
-      </c>
-      <c r="B63" t="s">
-        <v>95</v>
-      </c>
-      <c r="C63" t="s">
-        <v>123</v>
-      </c>
-      <c r="D63" t="s">
-        <v>158</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920252</v>
-      </c>
-      <c r="B64" t="s">
-        <v>96</v>
-      </c>
-      <c r="C64" t="s">
-        <v>124</v>
-      </c>
-      <c r="D64" t="s">
-        <v>159</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920252</v>
-      </c>
-      <c r="B65" t="s">
-        <v>96</v>
-      </c>
-      <c r="C65" t="s">
-        <v>124</v>
-      </c>
-      <c r="D65" t="s">
-        <v>159</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920253</v>
-      </c>
-      <c r="B66" t="s">
-        <v>96</v>
-      </c>
-      <c r="C66" t="s">
-        <v>125</v>
-      </c>
-      <c r="D66" t="s">
-        <v>160</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920253</v>
-      </c>
-      <c r="B67" t="s">
-        <v>96</v>
-      </c>
-      <c r="C67" t="s">
-        <v>125</v>
-      </c>
-      <c r="D67" t="s">
-        <v>160</v>
-      </c>
-      <c r="E67" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>20330051920256</v>
-      </c>
-      <c r="B68" t="s">
-        <v>97</v>
-      </c>
-      <c r="C68" t="s">
-        <v>126</v>
-      </c>
-      <c r="D68" t="s">
-        <v>161</v>
-      </c>
-      <c r="E68" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>20330051920256</v>
-      </c>
-      <c r="B69" t="s">
-        <v>97</v>
-      </c>
-      <c r="C69" t="s">
-        <v>126</v>
-      </c>
-      <c r="D69" t="s">
-        <v>161</v>
-      </c>
-      <c r="E69" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>20330051920257</v>
-      </c>
-      <c r="B70" t="s">
-        <v>98</v>
-      </c>
-      <c r="C70" t="s">
-        <v>127</v>
-      </c>
-      <c r="D70" t="s">
-        <v>162</v>
-      </c>
-      <c r="E70" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920257</v>
-      </c>
-      <c r="B71" t="s">
-        <v>98</v>
-      </c>
-      <c r="C71" t="s">
-        <v>127</v>
-      </c>
-      <c r="D71" t="s">
-        <v>162</v>
-      </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920258</v>
-      </c>
-      <c r="B72" t="s">
-        <v>99</v>
-      </c>
-      <c r="C72" t="s">
-        <v>99</v>
-      </c>
-      <c r="D72" t="s">
-        <v>163</v>
-      </c>
-      <c r="E72" t="s">
-        <v>6</v>
-      </c>
-      <c r="F72" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920258</v>
-      </c>
-      <c r="B73" t="s">
-        <v>99</v>
-      </c>
-      <c r="C73" t="s">
-        <v>99</v>
-      </c>
-      <c r="D73" t="s">
-        <v>163</v>
-      </c>
-      <c r="E73" t="s">
-        <v>7</v>
-      </c>
-      <c r="F73" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920259</v>
-      </c>
-      <c r="B74" t="s">
-        <v>99</v>
-      </c>
-      <c r="C74" t="s">
-        <v>99</v>
-      </c>
-      <c r="D74" t="s">
-        <v>164</v>
-      </c>
-      <c r="E74" t="s">
-        <v>6</v>
-      </c>
-      <c r="F74" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920259</v>
-      </c>
-      <c r="B75" t="s">
-        <v>99</v>
-      </c>
-      <c r="C75" t="s">
-        <v>99</v>
-      </c>
-      <c r="D75" t="s">
-        <v>164</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -6118,16 +4864,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920187</v>
+        <v>20330051920222</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -6135,16 +4881,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920220</v>
+        <v>20330051920251</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -6152,16 +4898,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920221</v>
+        <v>20330051920259</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -6169,580 +4915,580 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920374</v>
+        <v>20330051920234</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920222</v>
+        <v>20330051920236</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920223</v>
+        <v>20330051920240</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920224</v>
+        <v>20330051920244</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920225</v>
+        <v>20330051920258</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920375</v>
+        <v>20330051920187</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
         <v>136</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920226</v>
+        <v>20330051920220</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
         <v>137</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920227</v>
+        <v>20330051920221</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
         <v>138</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920228</v>
+        <v>20330051920374</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
         <v>139</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920229</v>
+        <v>20330051920223</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
         <v>140</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920230</v>
+        <v>20330051920224</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D15" t="s">
         <v>141</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920231</v>
+        <v>20330051920225</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
         <v>142</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920232</v>
+        <v>20330051920375</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
         <v>143</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920233</v>
+        <v>20330051920226</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
         <v>144</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920234</v>
+        <v>20330051920227</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920376</v>
+        <v>20330051920228</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
         <v>146</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920236</v>
+        <v>20330051920229</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
         <v>147</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920237</v>
+        <v>20330051920230</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>148</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920238</v>
+        <v>20330051920231</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920239</v>
+        <v>20330051920232</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
         <v>150</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920240</v>
+        <v>20330051920233</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
         <v>151</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920241</v>
+        <v>20330051920376</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
         <v>152</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920243</v>
+        <v>20330051920237</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
         <v>153</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920244</v>
+        <v>20330051920238</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
         <v>154</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920248</v>
+        <v>20330051920239</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D29" t="s">
         <v>155</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920249</v>
+        <v>20330051920241</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
         <v>156</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920250</v>
+        <v>20330051920243</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920251</v>
+        <v>20330051920248</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920252</v>
+        <v>20330051920249</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920253</v>
+        <v>20330051920250</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
         <v>160</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920256</v>
+        <v>20330051920252</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
         <v>161</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920257</v>
+        <v>20330051920253</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20330051920258</v>
+        <v>20330051920256</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
         <v>163</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>20330051920259</v>
+        <v>20330051920257</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
         <v>164</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6752,7 +5498,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6784,45 +5530,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920187</v>
+        <v>20330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920187</v>
+        <v>20330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6830,111 +5576,111 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920220</v>
+        <v>20330051920221</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920220</v>
+        <v>20330051920374</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920223</v>
+        <v>20330051920228</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920223</v>
+        <v>20330051920233</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>60</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920224</v>
+        <v>20330051920234</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>59</v>
@@ -6945,42 +5691,42 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920224</v>
+        <v>20330051920237</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>60</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920225</v>
+        <v>20330051920240</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>59</v>
@@ -6991,42 +5737,42 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920225</v>
+        <v>20330051920241</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>60</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920375</v>
+        <v>20330051920244</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>59</v>
@@ -7037,990 +5783,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920375</v>
+        <v>20330051920258</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920226</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" t="s">
-        <v>137</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920226</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920227</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920227</v>
-      </c>
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920229</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920229</v>
-      </c>
-      <c r="B19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920230</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920230</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920231</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" t="s">
-        <v>142</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920231</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920232</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920232</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920234</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920234</v>
-      </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920376</v>
-      </c>
-      <c r="B28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28" t="s">
-        <v>146</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920376</v>
-      </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" t="s">
-        <v>146</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920238</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" t="s">
-        <v>149</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920238</v>
-      </c>
-      <c r="B31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" t="s">
-        <v>149</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920239</v>
-      </c>
-      <c r="B32" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920239</v>
-      </c>
-      <c r="B33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" t="s">
-        <v>150</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>20330051920240</v>
-      </c>
-      <c r="B34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" t="s">
-        <v>120</v>
-      </c>
-      <c r="D34" t="s">
-        <v>151</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920240</v>
-      </c>
-      <c r="B35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" t="s">
-        <v>151</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>60</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>20330051920243</v>
-      </c>
-      <c r="B36" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" t="s">
-        <v>78</v>
-      </c>
-      <c r="D36" t="s">
-        <v>153</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>20330051920243</v>
-      </c>
-      <c r="B37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" t="s">
-        <v>153</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>20330051920244</v>
-      </c>
-      <c r="B38" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" t="s">
-        <v>113</v>
-      </c>
-      <c r="D38" t="s">
-        <v>154</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>20330051920244</v>
-      </c>
-      <c r="B39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" t="s">
-        <v>113</v>
-      </c>
-      <c r="D39" t="s">
-        <v>154</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>20330051920248</v>
-      </c>
-      <c r="B40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" t="s">
-        <v>155</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>59</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>20330051920248</v>
-      </c>
-      <c r="B41" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" t="s">
-        <v>155</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>20330051920249</v>
-      </c>
-      <c r="B42" t="s">
-        <v>93</v>
-      </c>
-      <c r="C42" t="s">
-        <v>122</v>
-      </c>
-      <c r="D42" t="s">
-        <v>156</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>59</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>20330051920249</v>
-      </c>
-      <c r="B43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" t="s">
-        <v>156</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>60</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>20330051920250</v>
-      </c>
-      <c r="B44" t="s">
-        <v>94</v>
-      </c>
-      <c r="C44" t="s">
-        <v>118</v>
-      </c>
-      <c r="D44" t="s">
-        <v>157</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>20330051920250</v>
-      </c>
-      <c r="B45" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" t="s">
-        <v>118</v>
-      </c>
-      <c r="D45" t="s">
-        <v>157</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>60</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>20330051920252</v>
-      </c>
-      <c r="B46" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" t="s">
-        <v>124</v>
-      </c>
-      <c r="D46" t="s">
-        <v>159</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>59</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>20330051920252</v>
-      </c>
-      <c r="B47" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" t="s">
-        <v>159</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>60</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>20330051920253</v>
-      </c>
-      <c r="B48" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" t="s">
-        <v>125</v>
-      </c>
-      <c r="D48" t="s">
-        <v>160</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>59</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>20330051920253</v>
-      </c>
-      <c r="B49" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" t="s">
-        <v>125</v>
-      </c>
-      <c r="D49" t="s">
-        <v>160</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>60</v>
-      </c>
-      <c r="G49">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>20330051920256</v>
-      </c>
-      <c r="B50" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50" t="s">
-        <v>126</v>
-      </c>
-      <c r="D50" t="s">
-        <v>161</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>59</v>
-      </c>
-      <c r="G50">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>20330051920256</v>
-      </c>
-      <c r="B51" t="s">
-        <v>97</v>
-      </c>
-      <c r="C51" t="s">
-        <v>126</v>
-      </c>
-      <c r="D51" t="s">
-        <v>161</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-      <c r="G51">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>20330051920257</v>
-      </c>
-      <c r="B52" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" t="s">
-        <v>162</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>59</v>
-      </c>
-      <c r="G52">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>20330051920257</v>
-      </c>
-      <c r="B53" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" t="s">
-        <v>127</v>
-      </c>
-      <c r="D53" t="s">
-        <v>162</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>60</v>
-      </c>
-      <c r="G53">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>20330051920258</v>
-      </c>
-      <c r="B54" t="s">
-        <v>99</v>
-      </c>
-      <c r="C54" t="s">
-        <v>99</v>
-      </c>
-      <c r="D54" t="s">
-        <v>163</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>59</v>
-      </c>
-      <c r="G54">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>20330051920258</v>
-      </c>
-      <c r="B55" t="s">
-        <v>99</v>
-      </c>
-      <c r="C55" t="s">
-        <v>99</v>
-      </c>
-      <c r="D55" t="s">
-        <v>163</v>
-      </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" t="s">
-        <v>60</v>
-      </c>
-      <c r="G55">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ALCM - Estadisticos 20212.xlsx
+++ b/grupos/4ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="163">
   <si>
     <t>Materia</t>
   </si>
@@ -167,9 +167,6 @@
     <t>XOTLANIHUA XOTLANIHUA ERIKA</t>
   </si>
   <si>
-    <t>XOTLANIHUA XOTLANIHUA JESUS URIEL</t>
-  </si>
-  <si>
     <t>Docente</t>
   </si>
   <si>
@@ -209,12 +206,12 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
-    <t>Ángel Martínez Noe Cristobal</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -285,9 +282,6 @@
   </si>
   <si>
     <t>ERIKA</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
   </si>
   <si>
     <t>ALVARADO</t>
@@ -870,7 +864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1038,7 +1032,7 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1047,13 +1041,13 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1089,7 +1083,7 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -1127,7 +1121,7 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1136,13 +1130,13 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1184,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1216,7 +1210,7 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1225,13 +1219,13 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1258,7 +1252,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1267,13 +1261,13 @@
         <v>10</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1305,7 +1299,7 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1314,13 +1308,13 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1356,13 +1350,13 @@
         <v>7</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1403,13 +1397,13 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1483,7 +1477,7 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1492,13 +1486,13 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1572,7 +1566,7 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1581,13 +1575,13 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1623,7 +1617,7 @@
         <v>9</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB10">
         <v>8</v>
@@ -1661,7 +1655,7 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1670,13 +1664,13 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1703,7 +1697,7 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1759,13 +1753,13 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1804,7 +1798,7 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1839,7 +1833,7 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1848,13 +1842,13 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1881,7 +1875,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1928,7 +1922,7 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1937,13 +1931,13 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1979,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -2017,7 +2011,7 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -2026,13 +2020,13 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2106,7 +2100,7 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -2115,13 +2109,13 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2148,7 +2142,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2157,7 +2151,7 @@
         <v>8</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>10</v>
@@ -2195,7 +2189,7 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2204,13 +2198,13 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2237,7 +2231,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -2284,7 +2278,7 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2293,13 +2287,13 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2373,7 +2367,7 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2382,13 +2376,13 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2415,7 +2409,7 @@
         <v>10</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2430,7 +2424,7 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2462,7 +2456,7 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2471,13 +2465,13 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2551,7 +2545,7 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2560,13 +2554,13 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2593,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -2640,7 +2634,7 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2649,13 +2643,13 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2729,7 +2723,7 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2738,13 +2732,13 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2818,7 +2812,7 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2827,13 +2821,13 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2907,7 +2901,7 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2916,13 +2910,13 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2958,13 +2952,13 @@
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB25">
         <v>9</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2996,7 +2990,7 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -3005,13 +2999,13 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -3085,7 +3079,7 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -3094,13 +3088,13 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3174,7 +3168,7 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -3183,13 +3177,13 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3216,7 +3210,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>-1</v>
@@ -3225,7 +3219,7 @@
         <v>6</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>8</v>
@@ -3263,7 +3257,7 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -3272,13 +3266,13 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3320,7 +3314,7 @@
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3352,7 +3346,7 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3361,13 +3355,13 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3409,7 +3403,7 @@
         <v>8</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3441,7 +3435,7 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3450,13 +3444,13 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3483,7 +3477,7 @@
         <v>6</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>-1</v>
@@ -3498,7 +3492,7 @@
         <v>9</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3530,7 +3524,7 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3539,13 +3533,13 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3619,7 +3613,7 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3628,13 +3622,13 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3670,7 +3664,7 @@
         <v>9</v>
       </c>
       <c r="AA33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB33">
         <v>10</v>
@@ -3708,7 +3702,7 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3717,13 +3711,13 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3750,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3765,7 +3759,7 @@
         <v>10</v>
       </c>
       <c r="AC34">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3797,7 +3791,7 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3806,13 +3800,13 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3851,10 +3845,10 @@
         <v>9</v>
       </c>
       <c r="AB35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3886,7 +3880,7 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3895,13 +3889,13 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3928,7 +3922,7 @@
         <v>8</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3937,7 +3931,7 @@
         <v>6</v>
       </c>
       <c r="AA36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB36">
         <v>10</v>
@@ -3975,7 +3969,7 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3984,13 +3978,13 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -4026,13 +4020,13 @@
         <v>10</v>
       </c>
       <c r="AA37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB37">
         <v>8</v>
       </c>
       <c r="AC37">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -4064,7 +4058,7 @@
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -4073,13 +4067,13 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -4162,13 +4156,13 @@
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -4211,95 +4205,6 @@
       </c>
       <c r="AC39">
         <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:29">
-      <c r="A40" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B40">
-        <v>5</v>
-      </c>
-      <c r="C40">
-        <v>-1</v>
-      </c>
-      <c r="D40">
-        <v>-1</v>
-      </c>
-      <c r="E40">
-        <v>6</v>
-      </c>
-      <c r="F40">
-        <v>5</v>
-      </c>
-      <c r="G40">
-        <v>6</v>
-      </c>
-      <c r="H40">
-        <v>5</v>
-      </c>
-      <c r="I40">
-        <v>-1</v>
-      </c>
-      <c r="J40">
-        <v>-1</v>
-      </c>
-      <c r="K40">
-        <v>-1</v>
-      </c>
-      <c r="L40">
-        <v>-1</v>
-      </c>
-      <c r="M40">
-        <v>-1</v>
-      </c>
-      <c r="N40">
-        <v>-1</v>
-      </c>
-      <c r="O40">
-        <v>-1</v>
-      </c>
-      <c r="P40">
-        <v>-1</v>
-      </c>
-      <c r="Q40">
-        <v>-1</v>
-      </c>
-      <c r="R40">
-        <v>-1</v>
-      </c>
-      <c r="S40">
-        <v>-1</v>
-      </c>
-      <c r="T40">
-        <v>-1</v>
-      </c>
-      <c r="U40">
-        <v>-1</v>
-      </c>
-      <c r="V40">
-        <v>-1</v>
-      </c>
-      <c r="W40">
-        <v>5</v>
-      </c>
-      <c r="X40">
-        <v>-1</v>
-      </c>
-      <c r="Y40">
-        <v>-1</v>
-      </c>
-      <c r="Z40">
-        <v>6</v>
-      </c>
-      <c r="AA40">
-        <v>5</v>
-      </c>
-      <c r="AB40">
-        <v>6</v>
-      </c>
-      <c r="AC40">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4326,31 +4231,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4358,10 +4263,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -4370,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>81.08</v>
+        <v>83.33</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -4379,10 +4284,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>18.92</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4390,22 +4295,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>6</v>
       </c>
       <c r="F3">
-        <v>83.78</v>
+        <v>83.33</v>
       </c>
       <c r="G3">
-        <v>16.22</v>
+        <v>16.67</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -4422,22 +4327,22 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4">
         <v>32</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>86.48999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="G4">
-        <v>13.51</v>
+        <v>11.11</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -4454,10 +4359,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5">
         <v>33</v>
@@ -4466,45 +4371,45 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>89.19</v>
+        <v>91.67</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>10.81</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>34</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="G6">
-        <v>8.109999999999999</v>
+        <v>5.56</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4515,28 +4420,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7">
         <v>34</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="G7">
-        <v>8.109999999999999</v>
+        <v>5.56</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4547,28 +4452,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>91.89</v>
+        <v>97.22</v>
       </c>
       <c r="G8">
-        <v>8.109999999999999</v>
+        <v>2.78</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4584,7 +4489,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4593,16 +4498,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4616,19 +4521,19 @@
         <v>20330051920222</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4636,19 +4541,19 @@
         <v>20330051920222</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4656,19 +4561,19 @@
         <v>20330051920234</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4676,19 +4581,19 @@
         <v>20330051920236</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4696,19 +4601,19 @@
         <v>20330051920240</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4716,19 +4621,19 @@
         <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4736,19 +4641,19 @@
         <v>20330051920251</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4756,19 +4661,19 @@
         <v>20330051920251</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4776,59 +4681,19 @@
         <v>20330051920258</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920259</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920259</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4838,7 +4703,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4847,19 +4712,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4867,13 +4732,13 @@
         <v>20330051920222</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -4884,13 +4749,13 @@
         <v>20330051920251</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -4898,24 +4763,24 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920259</v>
+        <v>20330051920234</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920234</v>
+        <v>20330051920236</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
@@ -4932,7 +4797,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920236</v>
+        <v>20330051920240</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
@@ -4949,7 +4814,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920240</v>
+        <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
@@ -4966,16 +4831,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920244</v>
+        <v>20330051920258</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4983,33 +4848,33 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920258</v>
+        <v>20330051920187</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920187</v>
+        <v>20330051920220</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -5017,16 +4882,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920220</v>
+        <v>20330051920221</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5034,16 +4899,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920221</v>
+        <v>20330051920374</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -5051,16 +4916,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920374</v>
+        <v>20330051920223</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5068,16 +4933,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920223</v>
+        <v>20330051920224</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -5085,16 +4950,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920224</v>
+        <v>20330051920225</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5102,16 +4967,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920225</v>
+        <v>20330051920375</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5119,16 +4984,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920375</v>
+        <v>20330051920226</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5136,16 +5001,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920226</v>
+        <v>20330051920227</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5153,16 +5018,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920227</v>
+        <v>20330051920228</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5170,16 +5035,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920228</v>
+        <v>20330051920229</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5187,16 +5052,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920229</v>
+        <v>20330051920230</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5204,16 +5069,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920230</v>
+        <v>20330051920231</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5221,16 +5086,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920231</v>
+        <v>20330051920232</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5238,16 +5103,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920232</v>
+        <v>20330051920233</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5255,16 +5120,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920233</v>
+        <v>20330051920376</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5272,16 +5137,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920376</v>
+        <v>20330051920237</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5289,16 +5154,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920237</v>
+        <v>20330051920238</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5306,16 +5171,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920238</v>
+        <v>20330051920239</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5323,16 +5188,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920239</v>
+        <v>20330051920241</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5340,16 +5205,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920241</v>
+        <v>20330051920243</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5357,16 +5222,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920243</v>
+        <v>20330051920248</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5374,16 +5239,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920248</v>
+        <v>20330051920249</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5391,16 +5256,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920249</v>
+        <v>20330051920250</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5408,16 +5273,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920250</v>
+        <v>20330051920252</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5425,16 +5290,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920252</v>
+        <v>20330051920253</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5442,16 +5307,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920253</v>
+        <v>20330051920256</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5459,35 +5324,18 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20330051920256</v>
+        <v>20330051920257</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>20330051920257</v>
-      </c>
-      <c r="B38" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" t="s">
-        <v>135</v>
-      </c>
-      <c r="D38" t="s">
-        <v>164</v>
-      </c>
-      <c r="E38">
         <v>0</v>
       </c>
     </row>
@@ -5498,7 +5346,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5507,22 +5355,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -5533,19 +5381,19 @@
         <v>20330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5556,19 +5404,19 @@
         <v>20330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5579,19 +5427,19 @@
         <v>20330051920221</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5599,22 +5447,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920374</v>
+        <v>20330051920228</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5622,22 +5470,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920228</v>
+        <v>20330051920233</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5645,162 +5493,139 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920233</v>
+        <v>20330051920234</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920234</v>
+        <v>20330051920237</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>59</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920237</v>
+        <v>20330051920240</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920240</v>
+        <v>20330051920241</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>59</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920241</v>
+        <v>20330051920244</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920244</v>
+        <v>20330051920258</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920258</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ALCM - Estadisticos 20212.xlsx
+++ b/grupos/4ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="163">
   <si>
     <t>Materia</t>
   </si>
@@ -194,18 +194,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Santiago Hernández Mariana</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Santiago Hernández Mariana</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
@@ -227,265 +227,265 @@
     <t>CAMARILLO</t>
   </si>
   <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>ERIKA</t>
+  </si>
+  <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>LASTRE</t>
+  </si>
+  <si>
     <t>LARRINAGA</t>
   </si>
   <si>
+    <t>LIMA</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TLECUILE</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CONDE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SALGADO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
   </si>
   <si>
     <t>SANTES</t>
   </si>
   <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>VANELY JUDITH</t>
+  </si>
+  <si>
+    <t>JOSSELIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>JOSE ISAIAS</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
+    <t>FERNANDA</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>JENIFER</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>VICTORINO</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ATENEA</t>
   </si>
   <si>
     <t>GONZALO FEDERICO</t>
   </si>
   <si>
+    <t>MERARY MADAY</t>
+  </si>
+  <si>
     <t>GENARO RAFAEL</t>
   </si>
   <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>CAROLINA</t>
+  </si>
+  <si>
+    <t>PERLA MARITZA</t>
+  </si>
+  <si>
     <t>DIEGO</t>
   </si>
   <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>LISBETH ESMERALDA</t>
+  </si>
+  <si>
     <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>ERIKA</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LASTRE</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TLECUILE</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>VANELY JUDITH</t>
-  </si>
-  <si>
-    <t>JOSSELIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>JUAN ALBERTO</t>
-  </si>
-  <si>
-    <t>JENIFER</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>VICTORINO</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ATENEA</t>
-  </si>
-  <si>
-    <t>MERARY MADAY</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>CAROLINA</t>
-  </si>
-  <si>
-    <t>PERLA MARITZA</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>LISBETH ESMERALDA</t>
   </si>
   <si>
     <t>FERNANDO VADHIR</t>
@@ -1029,16 +1029,16 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1071,13 +1071,13 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -1118,16 +1118,16 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -1160,7 +1160,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -1169,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>9</v>
@@ -1207,16 +1207,16 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -1249,16 +1249,16 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1296,16 +1296,16 @@
         <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1338,7 +1338,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -1347,7 +1347,7 @@
         <v>8</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>8</v>
@@ -1370,7 +1370,7 @@
         <v>-1</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1385,16 +1385,16 @@
         <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -1433,7 +1433,7 @@
         <v>-1</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -1474,16 +1474,16 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -1563,16 +1563,16 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1605,7 +1605,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1614,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA10">
         <v>7</v>
@@ -1652,16 +1652,16 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>9</v>
@@ -1694,7 +1694,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1703,7 +1703,7 @@
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA11">
         <v>10</v>
@@ -1726,7 +1726,7 @@
         <v>-1</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E12">
         <v>5</v>
@@ -1741,16 +1741,16 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1830,16 +1830,16 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -1872,7 +1872,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1919,16 +1919,16 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1967,10 +1967,10 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -2008,16 +2008,16 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>10</v>
@@ -2097,16 +2097,16 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -2145,10 +2145,10 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16">
         <v>9</v>
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>9</v>
@@ -2275,16 +2275,16 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>9</v>
@@ -2326,7 +2326,7 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA18">
         <v>9</v>
@@ -2364,16 +2364,16 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -2406,7 +2406,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2415,7 +2415,7 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>10</v>
@@ -2453,16 +2453,16 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>9</v>
@@ -2501,7 +2501,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z20">
         <v>10</v>
@@ -2527,7 +2527,7 @@
         <v>10</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>6</v>
@@ -2542,16 +2542,16 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -2590,10 +2590,10 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>9</v>
@@ -2631,16 +2631,16 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -2679,7 +2679,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2720,16 +2720,16 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2809,16 +2809,16 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>8</v>
@@ -2851,7 +2851,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -2860,7 +2860,7 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA24">
         <v>8</v>
@@ -2898,16 +2898,16 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -2940,7 +2940,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2987,16 +2987,16 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -3029,13 +3029,13 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z26">
         <v>10</v>
@@ -3061,7 +3061,7 @@
         <v>9</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>9</v>
@@ -3082,10 +3082,10 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -3124,10 +3124,10 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -3150,7 +3150,7 @@
         <v>10</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>6</v>
@@ -3165,16 +3165,16 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>9</v>
@@ -3213,7 +3213,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>6</v>
@@ -3254,16 +3254,16 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>8</v>
@@ -3302,10 +3302,10 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>8</v>
@@ -3343,16 +3343,16 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>8</v>
@@ -3394,7 +3394,7 @@
         <v>9</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA30">
         <v>9</v>
@@ -3417,7 +3417,7 @@
         <v>9</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>7</v>
@@ -3432,16 +3432,16 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -3474,13 +3474,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z31">
         <v>7</v>
@@ -3521,16 +3521,16 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -3563,7 +3563,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3610,16 +3610,16 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
         <v>9</v>
@@ -3652,7 +3652,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3699,16 +3699,16 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>9</v>
@@ -3741,16 +3741,16 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>9</v>
@@ -3788,16 +3788,16 @@
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>9</v>
@@ -3836,10 +3836,10 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA35">
         <v>9</v>
@@ -3877,16 +3877,16 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
         <v>9</v>
@@ -3919,16 +3919,16 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA36">
         <v>9</v>
@@ -3966,16 +3966,16 @@
         <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
         <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>10</v>
@@ -4008,7 +4008,7 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>8</v>
@@ -4055,16 +4055,16 @@
         <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J38">
         <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
         <v>10</v>
@@ -4097,7 +4097,7 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -4144,16 +4144,16 @@
         <v>9</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
         <v>10</v>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -4269,25 +4269,25 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>77.78</v>
+      </c>
+      <c r="G2">
+        <v>22.22</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>83.33</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2">
-        <v>16.67</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4301,19 +4301,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="G3">
-        <v>16.67</v>
+        <v>11.11</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -4333,30 +4333,30 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>88.89</v>
+        <v>91.67</v>
       </c>
       <c r="G4">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -4368,22 +4368,22 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>91.67</v>
       </c>
       <c r="G5">
+        <v>8.33</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="H5">
-        <v>8.9</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
       <c r="J5">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4489,7 +4489,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4524,176 +4524,56 @@
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920222</v>
+        <v>20330051920251</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920234</v>
+        <v>20330051920258</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920236</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920240</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920244</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920251</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920251</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920258</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4735,13 +4615,13 @@
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4749,30 +4629,30 @@
         <v>20330051920251</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920234</v>
+        <v>20330051920258</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -4780,81 +4660,81 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920236</v>
+        <v>20330051920187</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920240</v>
+        <v>20330051920220</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920244</v>
+        <v>20330051920221</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920258</v>
+        <v>20330051920374</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920187</v>
+        <v>20330051920223</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
         <v>134</v>
@@ -4865,13 +4745,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920220</v>
+        <v>20330051920224</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
         <v>135</v>
@@ -4882,13 +4762,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920221</v>
+        <v>20330051920225</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
         <v>136</v>
@@ -4899,13 +4779,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920374</v>
+        <v>20330051920375</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
         <v>137</v>
@@ -4916,13 +4796,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920223</v>
+        <v>20330051920226</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
         <v>138</v>
@@ -4933,13 +4813,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920224</v>
+        <v>20330051920227</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
         <v>139</v>
@@ -4950,13 +4830,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920225</v>
+        <v>20330051920228</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
         <v>140</v>
@@ -4967,13 +4847,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920375</v>
+        <v>20330051920229</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
         <v>141</v>
@@ -4984,13 +4864,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920226</v>
+        <v>20330051920230</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
         <v>142</v>
@@ -5001,13 +4881,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920227</v>
+        <v>20330051920231</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
         <v>143</v>
@@ -5018,13 +4898,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920228</v>
+        <v>20330051920232</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
         <v>144</v>
@@ -5035,13 +4915,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920229</v>
+        <v>20330051920233</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
         <v>145</v>
@@ -5052,13 +4932,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920230</v>
+        <v>20330051920234</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D21" t="s">
         <v>146</v>
@@ -5069,13 +4949,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920231</v>
+        <v>20330051920376</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
         <v>147</v>
@@ -5086,13 +4966,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920232</v>
+        <v>20330051920236</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
         <v>148</v>
@@ -5103,13 +4983,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920233</v>
+        <v>20330051920237</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
         <v>149</v>
@@ -5120,13 +5000,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920376</v>
+        <v>20330051920238</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
         <v>150</v>
@@ -5137,13 +5017,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920237</v>
+        <v>20330051920239</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
         <v>151</v>
@@ -5154,13 +5034,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920238</v>
+        <v>20330051920240</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s">
         <v>152</v>
@@ -5171,13 +5051,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920239</v>
+        <v>20330051920241</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s">
         <v>153</v>
@@ -5188,13 +5068,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920241</v>
+        <v>20330051920243</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s">
         <v>154</v>
@@ -5205,13 +5085,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920243</v>
+        <v>20330051920244</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
         <v>155</v>
@@ -5225,10 +5105,10 @@
         <v>20330051920248</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
         <v>156</v>
@@ -5242,10 +5122,10 @@
         <v>20330051920249</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
         <v>157</v>
@@ -5259,10 +5139,10 @@
         <v>20330051920250</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
         <v>158</v>
@@ -5276,10 +5156,10 @@
         <v>20330051920252</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
         <v>159</v>
@@ -5293,10 +5173,10 @@
         <v>20330051920253</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
         <v>160</v>
@@ -5310,10 +5190,10 @@
         <v>20330051920256</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
         <v>161</v>
@@ -5327,10 +5207,10 @@
         <v>20330051920257</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
         <v>162</v>
@@ -5346,7 +5226,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5378,22 +5258,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920236</v>
+        <v>20330051920237</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5401,45 +5281,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920236</v>
+        <v>20330051920237</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920221</v>
+        <v>20330051920225</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
         <v>136</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5447,22 +5327,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920228</v>
+        <v>20330051920375</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5470,22 +5350,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920233</v>
+        <v>20330051920228</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5493,45 +5373,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920234</v>
+        <v>20330051920233</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920237</v>
+        <v>20330051920234</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5539,45 +5419,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920240</v>
+        <v>20330051920236</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>58</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920241</v>
+        <v>20330051920244</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5585,47 +5465,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920244</v>
+        <v>20330051920258</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920258</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ALCM - Estadisticos 20212.xlsx
+++ b/grupos/4ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="163">
   <si>
     <t>Materia</t>
   </si>
@@ -197,16 +197,16 @@
     <t>Santiago Hernández Mariana</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
+    <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
     <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
@@ -1056,19 +1056,19 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1080,10 +1080,10 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -1145,19 +1145,19 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -1166,19 +1166,19 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB5">
         <v>8</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1234,19 +1234,19 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1258,16 +1258,16 @@
         <v>6</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB6">
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1323,19 +1323,19 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1347,13 +1347,13 @@
         <v>8</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>8</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1412,19 +1412,19 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1442,7 +1442,7 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1501,19 +1501,19 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1525,16 +1525,16 @@
         <v>8</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1590,19 +1590,19 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1614,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>7</v>
@@ -1623,7 +1623,7 @@
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1679,19 +1679,19 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1703,16 +1703,16 @@
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1768,19 +1768,19 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1798,7 +1798,7 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1857,19 +1857,19 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1881,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1946,19 +1946,19 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1967,19 +1967,19 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -2035,19 +2035,19 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -2124,19 +2124,19 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -2148,16 +2148,16 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB16">
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2213,19 +2213,19 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2237,16 +2237,16 @@
         <v>9</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2302,19 +2302,19 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2323,10 +2323,10 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>9</v>
@@ -2391,19 +2391,19 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2412,13 +2412,13 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB19">
         <v>10</v>
@@ -2480,19 +2480,19 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2504,10 +2504,10 @@
         <v>9</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB20">
         <v>10</v>
@@ -2569,19 +2569,19 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2590,13 +2590,13 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z21">
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -2658,19 +2658,19 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2682,7 +2682,7 @@
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>7</v>
@@ -2691,7 +2691,7 @@
         <v>10</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2747,19 +2747,19 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2836,19 +2836,19 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2860,10 +2860,10 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>8</v>
@@ -2925,19 +2925,19 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2949,10 +2949,10 @@
         <v>6</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB25">
         <v>9</v>
@@ -3014,19 +3014,19 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -3035,7 +3035,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>10</v>
@@ -3047,7 +3047,7 @@
         <v>10</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3103,19 +3103,19 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -3124,19 +3124,19 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3192,19 +3192,19 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -3213,19 +3213,19 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB28">
         <v>8</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3281,19 +3281,19 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3370,19 +3370,19 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -3391,19 +3391,19 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>8</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3459,19 +3459,19 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>5</v>
@@ -3483,7 +3483,7 @@
         <v>6</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA31">
         <v>7</v>
@@ -3548,19 +3548,19 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3637,19 +3637,19 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3664,13 +3664,13 @@
         <v>9</v>
       </c>
       <c r="AA33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB33">
         <v>10</v>
       </c>
       <c r="AC33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3726,19 +3726,19 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3747,19 +3747,19 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>7</v>
       </c>
       <c r="AA34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB34">
         <v>10</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3815,19 +3815,19 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -3839,7 +3839,7 @@
         <v>7</v>
       </c>
       <c r="Z35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA35">
         <v>9</v>
@@ -3904,19 +3904,19 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3925,19 +3925,19 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB36">
         <v>10</v>
       </c>
       <c r="AC36">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3993,19 +3993,19 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -4017,13 +4017,13 @@
         <v>9</v>
       </c>
       <c r="Z37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA37">
         <v>9</v>
       </c>
       <c r="AB37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC37">
         <v>9</v>
@@ -4082,19 +4082,19 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W38">
         <v>8</v>
@@ -4106,7 +4106,7 @@
         <v>9</v>
       </c>
       <c r="Z38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA38">
         <v>10</v>
@@ -4171,19 +4171,19 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W39">
         <v>6</v>
@@ -4195,13 +4195,13 @@
         <v>9</v>
       </c>
       <c r="Z39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC39">
         <v>9</v>
@@ -4292,7 +4292,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -4301,30 +4301,30 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>88.89</v>
+        <v>91.67</v>
       </c>
       <c r="G3">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -4333,30 +4333,30 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>94.44</v>
+      </c>
+      <c r="G4">
+        <v>5.56</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>91.67</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>8.9</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>8.33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -4365,19 +4365,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="G5">
-        <v>8.33</v>
+        <v>5.56</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4388,10 +4388,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>36</v>
@@ -4409,7 +4409,7 @@
         <v>5.56</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -4429,19 +4429,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="G7">
-        <v>5.56</v>
+        <v>2.78</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>97.22</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4533,7 +4533,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4553,7 +4553,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4573,7 +4573,7 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -5226,7 +5226,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5258,16 +5258,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920237</v>
+        <v>20330051920225</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5281,22 +5281,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920237</v>
+        <v>20330051920375</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5304,16 +5304,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920225</v>
+        <v>20330051920228</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5327,16 +5327,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920375</v>
+        <v>20330051920236</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -5350,16 +5350,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920228</v>
+        <v>20330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5373,22 +5373,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920233</v>
+        <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5396,93 +5396,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920234</v>
+        <v>20330051920258</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920236</v>
-      </c>
-      <c r="B9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920244</v>
-      </c>
-      <c r="B10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920258</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ALCM - Estadisticos 20212.xlsx
+++ b/grupos/4ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="163">
   <si>
     <t>Materia</t>
   </si>
@@ -197,18 +197,18 @@
     <t>Santiago Hernández Mariana</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -224,289 +224,289 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
     <t>CAMARILLO</t>
   </si>
   <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>LASTRE</t>
+  </si>
+  <si>
+    <t>LARRINAGA</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TLECUILE</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>SORIA</t>
   </si>
   <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CONDE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SALGADO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>SANTES</t>
+  </si>
+  <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>VANELY JUDITH</t>
+  </si>
+  <si>
+    <t>JOSSELIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>JOSE ISAIAS</t>
+  </si>
+  <si>
     <t>ARIEL</t>
   </si>
   <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
+    <t>FERNANDA</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>JENIFER</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>VICTORINO</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ATENEA</t>
+  </si>
+  <si>
+    <t>GONZALO FEDERICO</t>
+  </si>
+  <si>
+    <t>MERARY MADAY</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>CAROLINA</t>
+  </si>
+  <si>
+    <t>PERLA MARITZA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>LISBETH ESMERALDA</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>FERNANDO VADHIR</t>
+  </si>
+  <si>
+    <t>CYNTHIA AIDEE</t>
+  </si>
+  <si>
+    <t>FABIOLA</t>
+  </si>
+  <si>
     <t>ANGEL EMMANUEL</t>
   </si>
   <si>
+    <t>ARLET</t>
+  </si>
+  <si>
+    <t>ROSARIO</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>SELINA</t>
+  </si>
+  <si>
     <t>ERIKA</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LASTRE</t>
-  </si>
-  <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TLECUILE</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>SANTES</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>VANELY JUDITH</t>
-  </si>
-  <si>
-    <t>JOSSELIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>JUAN ALBERTO</t>
-  </si>
-  <si>
-    <t>JENIFER</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>VICTORINO</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ATENEA</t>
-  </si>
-  <si>
-    <t>GONZALO FEDERICO</t>
-  </si>
-  <si>
-    <t>MERARY MADAY</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>CAROLINA</t>
-  </si>
-  <si>
-    <t>PERLA MARITZA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>LISBETH ESMERALDA</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>FERNANDO VADHIR</t>
-  </si>
-  <si>
-    <t>CYNTHIA AIDEE</t>
-  </si>
-  <si>
-    <t>FABIOLA</t>
-  </si>
-  <si>
-    <t>ARLET</t>
-  </si>
-  <si>
-    <t>ROSARIO</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>SELINA</t>
   </si>
 </sst>
 </file>
@@ -1050,10 +1050,10 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1139,10 +1139,10 @@
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>6</v>
@@ -1163,7 +1163,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1228,10 +1228,10 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -1249,10 +1249,10 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1317,10 +1317,10 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>9</v>
@@ -1338,7 +1338,7 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -1367,7 +1367,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -1388,7 +1388,7 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -1406,10 +1406,10 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>5</v>
@@ -1430,7 +1430,7 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1495,10 +1495,10 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>9</v>
@@ -1584,10 +1584,10 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -1605,7 +1605,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1673,10 +1673,10 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>8</v>
@@ -1694,10 +1694,10 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1723,7 +1723,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -1744,7 +1744,7 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -1762,10 +1762,10 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -1786,7 +1786,7 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1851,10 +1851,10 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -1872,10 +1872,10 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1940,10 +1940,10 @@
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>8</v>
@@ -2029,10 +2029,10 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>10</v>
@@ -2118,10 +2118,10 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>7</v>
@@ -2207,10 +2207,10 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -2231,7 +2231,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -2296,10 +2296,10 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>5</v>
@@ -2320,7 +2320,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2385,10 +2385,10 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>7</v>
@@ -2406,7 +2406,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2474,10 +2474,10 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>9</v>
@@ -2563,10 +2563,10 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -2587,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2652,10 +2652,10 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>9</v>
@@ -2673,7 +2673,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2741,10 +2741,10 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>9</v>
@@ -2830,10 +2830,10 @@
         <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
         <v>8</v>
@@ -2919,10 +2919,10 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>7</v>
@@ -2940,10 +2940,10 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -3008,10 +3008,10 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -3076,7 +3076,7 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>9</v>
@@ -3097,10 +3097,10 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>6</v>
@@ -3186,10 +3186,10 @@
         <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>8</v>
@@ -3207,10 +3207,10 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -3275,10 +3275,10 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>7</v>
@@ -3296,7 +3296,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3364,10 +3364,10 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
         <v>8</v>
@@ -3453,10 +3453,10 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>6</v>
@@ -3474,7 +3474,7 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3542,10 +3542,10 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>9</v>
@@ -3631,10 +3631,10 @@
         <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>9</v>
@@ -3720,10 +3720,10 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -3809,10 +3809,10 @@
         <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>7</v>
@@ -3830,7 +3830,7 @@
         <v>7</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3898,10 +3898,10 @@
         <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>9</v>
@@ -3919,7 +3919,7 @@
         <v>6</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>9</v>
@@ -3987,10 +3987,10 @@
         <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
         <v>9</v>
@@ -4076,10 +4076,10 @@
         <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>9</v>
@@ -4126,7 +4126,7 @@
         <v>6</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D39">
         <v>9</v>
@@ -4147,7 +4147,7 @@
         <v>6</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
         <v>9</v>
@@ -4165,10 +4165,10 @@
         <v>9</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>9</v>
@@ -4186,10 +4186,10 @@
         <v>8</v>
       </c>
       <c r="W39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>9</v>
@@ -4269,19 +4269,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>77.78</v>
+        <v>91.67</v>
       </c>
       <c r="G2">
-        <v>22.22</v>
+        <v>8.33</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4292,7 +4292,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -4301,30 +4301,30 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -4345,7 +4345,7 @@
         <v>5.56</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5">
         <v>36</v>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -4397,19 +4397,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="G6">
-        <v>5.56</v>
+        <v>2.78</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -4429,19 +4429,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>97.22</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4489,7 +4489,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4514,66 +4514,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920222</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920251</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920258</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4609,64 +4549,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920222</v>
+        <v>20330051920187</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920251</v>
+        <v>20330051920220</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920258</v>
+        <v>20330051920221</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920187</v>
+        <v>20330051920374</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
         <v>130</v>
@@ -4677,13 +4617,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920220</v>
+        <v>20330051920222</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
         <v>131</v>
@@ -4694,13 +4634,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920221</v>
+        <v>20330051920223</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
         <v>132</v>
@@ -4711,13 +4651,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920374</v>
+        <v>20330051920224</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
         <v>133</v>
@@ -4728,13 +4668,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920223</v>
+        <v>20330051920225</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
         <v>134</v>
@@ -4745,13 +4685,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920224</v>
+        <v>20330051920375</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
         <v>135</v>
@@ -4762,13 +4702,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920225</v>
+        <v>20330051920226</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
         <v>136</v>
@@ -4779,13 +4719,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920375</v>
+        <v>20330051920227</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
         <v>137</v>
@@ -4796,13 +4736,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920226</v>
+        <v>20330051920228</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
         <v>138</v>
@@ -4813,13 +4753,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920227</v>
+        <v>20330051920229</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
         <v>139</v>
@@ -4830,13 +4770,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920228</v>
+        <v>20330051920230</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
         <v>140</v>
@@ -4847,13 +4787,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920229</v>
+        <v>20330051920231</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
         <v>141</v>
@@ -4864,13 +4804,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920230</v>
+        <v>20330051920232</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
         <v>142</v>
@@ -4881,13 +4821,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920231</v>
+        <v>20330051920233</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
         <v>143</v>
@@ -4898,13 +4838,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920232</v>
+        <v>20330051920234</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
         <v>144</v>
@@ -4915,13 +4855,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920233</v>
+        <v>20330051920376</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
         <v>145</v>
@@ -4932,13 +4872,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920234</v>
+        <v>20330051920236</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
         <v>146</v>
@@ -4949,13 +4889,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920376</v>
+        <v>20330051920237</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
         <v>147</v>
@@ -4966,13 +4906,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920236</v>
+        <v>20330051920238</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
         <v>148</v>
@@ -4983,13 +4923,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920237</v>
+        <v>20330051920239</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
         <v>149</v>
@@ -5000,13 +4940,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920238</v>
+        <v>20330051920240</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
         <v>150</v>
@@ -5017,13 +4957,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920239</v>
+        <v>20330051920241</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
         <v>151</v>
@@ -5034,13 +4974,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920240</v>
+        <v>20330051920243</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
         <v>152</v>
@@ -5051,13 +4991,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920241</v>
+        <v>20330051920244</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
         <v>153</v>
@@ -5068,13 +5008,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920243</v>
+        <v>20330051920248</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
         <v>154</v>
@@ -5085,13 +5025,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920244</v>
+        <v>20330051920249</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
         <v>155</v>
@@ -5102,13 +5042,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920248</v>
+        <v>20330051920250</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
         <v>156</v>
@@ -5119,13 +5059,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920249</v>
+        <v>20330051920251</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
         <v>157</v>
@@ -5136,13 +5076,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920250</v>
+        <v>20330051920252</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
         <v>158</v>
@@ -5153,13 +5093,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920252</v>
+        <v>20330051920253</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
         <v>159</v>
@@ -5170,13 +5110,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920253</v>
+        <v>20330051920256</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D35" t="s">
         <v>160</v>
@@ -5187,13 +5127,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920256</v>
+        <v>20330051920257</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
         <v>161</v>
@@ -5204,13 +5144,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20330051920257</v>
+        <v>20330051920258</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
         <v>162</v>
@@ -5226,7 +5166,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5258,16 +5198,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920225</v>
+        <v>20330051920228</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5277,144 +5217,6 @@
       </c>
       <c r="G2">
         <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920375</v>
-      </c>
-      <c r="B3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920228</v>
-      </c>
-      <c r="B4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920236</v>
-      </c>
-      <c r="B5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920237</v>
-      </c>
-      <c r="B6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920244</v>
-      </c>
-      <c r="B7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920258</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>
